--- a/ig/test-tabs-svs/ValueSet-jdv-modele-document-cda.xlsx
+++ b/ig/test-tabs-svs/ValueSet-jdv-modele-document-cda.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T08:46:20+00:00</t>
+    <t>2026-06-01T09:57:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/test-tabs-svs/ValueSet-jdv-modele-document-cda.xlsx
+++ b/ig/test-tabs-svs/ValueSet-jdv-modele-document-cda.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T09:57:24+00:00</t>
+    <t>2026-06-01T12:34:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/test-tabs-svs/ValueSet-jdv-modele-document-cda.xlsx
+++ b/ig/test-tabs-svs/ValueSet-jdv-modele-document-cda.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T12:34:00+00:00</t>
+    <t>2026-06-01T13:24:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/test-tabs-svs/ValueSet-jdv-modele-document-cda.xlsx
+++ b/ig/test-tabs-svs/ValueSet-jdv-modele-document-cda.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T13:24:12+00:00</t>
+    <t>2026-06-02T13:13:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/test-tabs-svs/ValueSet-jdv-modele-document-cda.xlsx
+++ b/ig/test-tabs-svs/ValueSet-jdv-modele-document-cda.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-02T13:13:17+00:00</t>
+    <t>2026-06-03T07:33:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/test-tabs-svs/ValueSet-jdv-modele-document-cda.xlsx
+++ b/ig/test-tabs-svs/ValueSet-jdv-modele-document-cda.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-03T07:33:02+00:00</t>
+    <t>2026-06-03T13:06:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/test-tabs-svs/ValueSet-jdv-modele-document-cda.xlsx
+++ b/ig/test-tabs-svs/ValueSet-jdv-modele-document-cda.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-03T13:06:48+00:00</t>
+    <t>2026-06-30T09:06:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
